--- a/SensitivityAnalysis/SingleSNP/MR_res_binaryLR.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_binaryLR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="18">
   <si>
     <t>id.exposure</t>
   </si>
@@ -44,15 +44,6 @@
   </si>
   <si>
     <t>pval</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>C1_L</t>
-  </si>
-  <si>
-    <t>C2_U</t>
   </si>
   <si>
     <t>1</t>
@@ -156,34 +147,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -196,15 +178,6 @@
       </c>
       <c r="J2" t="n">
         <v>2.098006599721131E-7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.12556238873447934</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.05735524921561809</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.27488178815924963</v>
       </c>
     </row>
   </sheetData>
@@ -246,34 +219,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -286,15 +250,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.29481479490083357</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.5486630493387519</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.6832258797777289</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.5103430818039985</v>
       </c>
     </row>
   </sheetData>
@@ -336,34 +291,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -376,15 +322,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.20405606765255724</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.912330437304899</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7031569864080136</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5.200841024312504</v>
       </c>
     </row>
   </sheetData>
@@ -426,34 +363,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -466,15 +394,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.9265850208984425</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.9300045568317372</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.19866286872384317</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4.353649382412201</v>
       </c>
     </row>
   </sheetData>
@@ -516,34 +435,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -556,15 +466,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.7835625219492152</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.0653457793358705</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.678155058414704</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.673601952040154</v>
       </c>
     </row>
   </sheetData>
@@ -606,34 +507,25 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -646,15 +538,6 @@
       </c>
       <c r="J2" t="n">
         <v>0.007231500464492473</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.7691024390061854</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.316918580201915</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5.822629001509213</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/SingleSNP/MR_res_binaryLR.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_binaryLR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="21">
   <si>
     <t>id.exposure</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>pval</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>CI_LOW_OR</t>
+  </si>
+  <si>
+    <t>CI_HIGH_OR</t>
   </si>
   <si>
     <t>1</t>
@@ -147,37 +156,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.0749525225439274</v>
+        <v>1.5778333502989363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3997644834553275</v>
+        <v>0.46219546357972835</v>
       </c>
       <c r="J2" t="n">
-        <v>2.098006599721131E-7</v>
+        <v>6.406842958793678E-4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2064218579009453</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.08343090631777333</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.510721809217609</v>
       </c>
     </row>
   </sheetData>
@@ -219,37 +246,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4373920099081709</v>
+        <v>-0.5239164319718362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4175111055595221</v>
+        <v>0.4866648102715735</v>
       </c>
       <c r="J2" t="n">
-        <v>0.29481479490083357</v>
+        <v>0.2816837118964371</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.688628113260208</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6505438353342711</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.38320179212451</v>
       </c>
     </row>
   </sheetData>
@@ -291,37 +336,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6483226225552706</v>
+        <v>-0.930175559896012</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5104580231627839</v>
+        <v>0.5992505859410162</v>
       </c>
       <c r="J2" t="n">
-        <v>0.20405606765255724</v>
+        <v>0.12060687181714269</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.5349541748462094</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7832090845597989</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.204696287686629</v>
       </c>
     </row>
   </sheetData>
@@ -363,37 +426,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07256579302776718</v>
+        <v>0.44708722345026414</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7875409310723104</v>
+        <v>0.9286688108937556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9265850208984425</v>
+        <v>0.6302122981891447</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6394881274812577</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.10359376930572015</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.9475836040160823</v>
       </c>
     </row>
   </sheetData>
@@ -435,37 +516,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06329942189846809</v>
+        <v>-0.23084313982096438</v>
       </c>
       <c r="I2" t="n">
-        <v>0.23044833640882828</v>
+        <v>0.26773855961745274</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7835625219492152</v>
+        <v>0.38857961977747774</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.2596616332020525</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7453328088767469</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.1289112880359697</v>
       </c>
     </row>
   </sheetData>
@@ -507,37 +606,55 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0185232384507856</v>
+        <v>-1.0830616824609844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.37919828559737695</v>
+        <v>0.4431061314679618</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007231500464492473</v>
+        <v>0.014515407766472005</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.953709040461439</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.239333412839837</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.039588383010146</v>
       </c>
     </row>
   </sheetData>
